--- a/data/employees/EMP068/AST-EMP068-06.xlsx
+++ b/data/employees/EMP068/AST-EMP068-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Budget Tracker - Jamie Brown (Finance)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Jamie Brown | Role: Analyst | Location: Austin | Date: 2025-03-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Cost Centre</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Budget ($K)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Actual ($K)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Variance ($K)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Variance %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>98</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CC-1001 Engineering</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2380</v>
-      </c>
-      <c r="D5" t="n">
-        <v>120</v>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>4.8</v>
+        <v>60</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Fabric semantic model planning. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CC-1002 Operations</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-120</v>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>-6.7</v>
+        <v>66</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Section 1: Knowledge transfer and onboarding. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CC-1003 R&amp;D</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3200</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3100</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100</v>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>3.1</v>
+        <v>80</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Knowledge transfer and onboarding. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CC-1004 IT</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1195</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>77</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Section 1: Quarterly delivery milestones. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>99</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>90</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>92</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>98</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>72</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>63</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>91</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>68</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>65</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>75</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>72</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>80</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>86</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>77</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>80</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>84</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp068 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>70</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP068</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP068 contributes to ast emp068 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>